--- a/Hardware/DC34_Cnet_Badge_BoMs.xlsx
+++ b/Hardware/DC34_Cnet_Badge_BoMs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Drive\Dev\Arduino\DC34_Cnet_Badge\Private\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Drive\Dev\Arduino\DC34_Cnet_Badge\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6A6E7B-E737-4518-8602-9109F1B92C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE5DBA4-E06A-4380-9495-35B9242BFC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15285" yWindow="2085" windowWidth="28155" windowHeight="18390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11820" yWindow="1290" windowWidth="28155" windowHeight="18390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DC34_Cnet_Badge" sheetId="1" r:id="rId1"/>
@@ -257,12 +257,6 @@
     <t>Total Order Cost</t>
   </si>
   <si>
-    <t>Total BadgeCost</t>
-  </si>
-  <si>
-    <t>Total SAO Cost</t>
-  </si>
-  <si>
     <t>https://www.digikey.com/en/products/detail/sparkfun-electronics/11450/5673784</t>
   </si>
   <si>
@@ -273,6 +267,12 @@
   </si>
   <si>
     <t>RGB LED - Fast Cycle - 3mm</t>
+  </si>
+  <si>
+    <t>Total Badges Cost</t>
+  </si>
+  <si>
+    <t>Total SAOs Cost</t>
   </si>
 </sst>
 </file>
@@ -663,7 +663,7 @@
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1191,7 +1191,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1297,7 +1297,7 @@
         <v>2977.7799999999997</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1333,7 +1333,7 @@
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -1860,7 +1860,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1891,7 +1891,7 @@
         <v>74.25</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1966,7 +1966,7 @@
         <v>2869.83</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2002,7 +2002,7 @@
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -2125,7 +2125,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -2267,7 +2267,7 @@
         <v>315.27</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2293,7 +2293,7 @@
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -2416,7 +2416,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -2447,7 +2447,7 @@
         <v>297</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -2522,7 +2522,7 @@
         <v>432.27000000000004</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
